--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2580645161290323</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="B2">
-        <v>0.01351351351351351</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3142857142857143</v>
+        <v>0.2464788732394366</v>
       </c>
       <c r="D2">
-        <v>0.9142857142857143</v>
+        <v>0.9224137931034483</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2647058823529412</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.01204819277108434</v>
       </c>
       <c r="C2">
-        <v>0.2464788732394366</v>
+        <v>0.2535211267605634</v>
       </c>
       <c r="D2">
-        <v>0.9224137931034483</v>
+        <v>0.954954954954955</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
